--- a/analysis/first_zero_duplicate_k_rerun/artifacts/default_run/concatenated/clustering_audit.xlsx
+++ b/analysis/first_zero_duplicate_k_rerun/artifacts/default_run/concatenated/clustering_audit.xlsx
@@ -212,9 +212,9 @@
     <tableColumn id="4" name="velocity"/>
     <tableColumn id="5" name="trial_num"/>
     <tableColumn id="6" name="trial_id"/>
-    <tableColumn id="7" name="cluster_id"/>
-    <tableColumn id="8" name="analysis_unit_id"/>
-    <tableColumn id="9" name="source_trial_nums_csv"/>
+    <tableColumn id="7" name="analysis_unit_id"/>
+    <tableColumn id="8" name="source_trial_nums_csv"/>
+    <tableColumn id="9" name="cluster_id"/>
     <tableColumn id="10" name="k"/>
     <tableColumn id="11" name="is_gap_raw_k"/>
     <tableColumn id="12" name="is_selected_k"/>
@@ -1674,9 +1674,9 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -4652,17 +4652,17 @@
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
+          <t>analysis_unit_id</t>
+        </is>
+      </c>
+      <c r="H55" s="1" t="inlineStr">
+        <is>
+          <t>source_trial_nums_csv</t>
+        </is>
+      </c>
+      <c r="I55" s="1" t="inlineStr">
+        <is>
           <t>cluster_id</t>
-        </is>
-      </c>
-      <c r="H55" s="1" t="inlineStr">
-        <is>
-          <t>analysis_unit_id</t>
-        </is>
-      </c>
-      <c r="I55" s="1" t="inlineStr">
-        <is>
-          <t>source_trial_nums_csv</t>
         </is>
       </c>
       <c r="J55" s="1" t="inlineStr">
@@ -4720,18 +4720,18 @@
           <t>권유영_v35.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G56" t="n">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
         <v>3</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J56" t="n">
         <v>7</v>
@@ -4780,18 +4780,18 @@
           <t>김서하_v130.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>2</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I57" t="n">
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>7</v>
@@ -4840,18 +4840,18 @@
           <t>김우연_v60.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G58" t="n">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
         <v>6</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J58" t="n">
         <v>7</v>
@@ -4900,18 +4900,18 @@
           <t>김우연_v60.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G59" t="n">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
         <v>5</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J59" t="n">
         <v>7</v>
@@ -4960,18 +4960,18 @@
           <t>김유민_v70.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G60" t="n">
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
         <v>1</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J60" t="n">
         <v>7</v>
@@ -5020,18 +5020,18 @@
           <t>방수진_v50.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G61" t="n">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
         <v>6</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J61" t="n">
         <v>7</v>
@@ -5080,18 +5080,18 @@
           <t>방수진_v50.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I62" t="n">
+        <v>0</v>
       </c>
       <c r="J62" t="n">
         <v>7</v>
@@ -5140,18 +5140,18 @@
           <t>오나영_v25.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>2</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I63" t="n">
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>7</v>
@@ -5200,18 +5200,18 @@
           <t>오나영_v25.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>2</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I64" t="n">
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>7</v>
@@ -5260,18 +5260,18 @@
           <t>유병한_v110.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>2</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I65" t="n">
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>7</v>
@@ -5320,18 +5320,18 @@
           <t>유병한_v110.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G66" t="n">
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
         <v>6</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J66" t="n">
         <v>7</v>
@@ -5380,18 +5380,18 @@
           <t>유재원_v45.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G67" t="n">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
         <v>6</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J67" t="n">
         <v>7</v>
@@ -5440,18 +5440,18 @@
           <t>유재원_v45.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>2</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I68" t="n">
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>7</v>
@@ -5500,18 +5500,18 @@
           <t>이은수_v35.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>2</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I69" t="n">
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>7</v>
@@ -5560,18 +5560,18 @@
           <t>이은수_v35.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G70" t="n">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
         <v>3</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J70" t="n">
         <v>7</v>
@@ -5620,18 +5620,18 @@
           <t>이은수_v35.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G71" t="n">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
         <v>4</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J71" t="n">
         <v>7</v>
@@ -5680,18 +5680,18 @@
           <t>이인섭_v30.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G72" t="n">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
         <v>3</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J72" t="n">
         <v>7</v>
@@ -5740,18 +5740,18 @@
           <t>이재유_v20.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>2</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I73" t="n">
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>7</v>
@@ -5800,18 +5800,18 @@
           <t>조민석_v30.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>2</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I74" t="n">
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>7</v>
@@ -5860,18 +5860,18 @@
           <t>조민석_v30.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G75" t="n">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
         <v>4</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J75" t="n">
         <v>7</v>
@@ -5920,18 +5920,18 @@
           <t>권유영_v35.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G76" t="n">
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
         <v>4</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J76" t="n">
         <v>8</v>
@@ -5980,18 +5980,18 @@
           <t>김서하_v130.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G77" t="n">
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
         <v>6</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J77" t="n">
         <v>8</v>
@@ -6040,18 +6040,18 @@
           <t>김우연_v60.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G78" t="n">
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
         <v>5</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J78" t="n">
         <v>8</v>
@@ -6100,18 +6100,18 @@
           <t>김유민_v70.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G79" t="n">
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
         <v>7</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J79" t="n">
         <v>8</v>
@@ -6160,18 +6160,18 @@
           <t>방수진_v50.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G80" t="n">
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
         <v>4</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J80" t="n">
         <v>8</v>
@@ -6220,18 +6220,18 @@
           <t>오나영_v25.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G81" t="n">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
         <v>6</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J81" t="n">
         <v>8</v>
@@ -6280,18 +6280,18 @@
           <t>유병한_v110.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G82" t="n">
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
         <v>5</v>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J82" t="n">
         <v>8</v>
@@ -6340,18 +6340,18 @@
           <t>유병한_v110.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G83" t="n">
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
         <v>6</v>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J83" t="n">
         <v>8</v>
@@ -6400,18 +6400,18 @@
           <t>유재원_v45.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G84" t="n">
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
         <v>6</v>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J84" t="n">
         <v>8</v>
@@ -6460,18 +6460,18 @@
           <t>이은수_v35.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G85" t="n">
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
         <v>1</v>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J85" t="n">
         <v>8</v>
@@ -6520,18 +6520,18 @@
           <t>이인섭_v30.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G86" t="n">
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
         <v>5</v>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J86" t="n">
         <v>8</v>
@@ -6580,18 +6580,18 @@
           <t>이재유_v20.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G87" t="n">
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
         <v>6</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J87" t="n">
         <v>8</v>
@@ -6640,18 +6640,18 @@
           <t>이지수_v130.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G88" t="n">
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
         <v>4</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J88" t="n">
         <v>8</v>
@@ -6700,18 +6700,18 @@
           <t>김민정_v20.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G89" t="n">
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
         <v>3</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J89" t="n">
         <v>9</v>
@@ -6760,18 +6760,18 @@
           <t>김우연_v60.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G90" t="n">
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
         <v>6</v>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J90" t="n">
         <v>9</v>
@@ -6820,18 +6820,18 @@
           <t>방수진_v50.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G91" t="n">
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
         <v>1</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J91" t="n">
         <v>9</v>
@@ -6880,18 +6880,18 @@
           <t>유병한_v110.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>2</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I92" t="n">
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>9</v>
@@ -6940,18 +6940,18 @@
           <t>이은수_v35.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G93" t="n">
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
         <v>7</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J93" t="n">
         <v>9</v>
@@ -7000,18 +7000,18 @@
           <t>이인섭_v30.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G94" t="n">
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
         <v>6</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J94" t="n">
         <v>9</v>
@@ -7060,18 +7060,18 @@
           <t>유병한_v110.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G95" t="n">
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
         <v>3</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J95" t="n">
         <v>10</v>
@@ -7120,18 +7120,18 @@
           <t>이은수_v35.0_Tconcat_nonstep</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="I96" t="n">
+        <v>0</v>
       </c>
       <c r="J96" t="n">
         <v>10</v>
@@ -7180,18 +7180,18 @@
           <t>조민석_v30.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G97" t="n">
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
         <v>7</v>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J97" t="n">
         <v>10</v>
@@ -7240,18 +7240,18 @@
           <t>김유민_v70.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G98" t="n">
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
         <v>7</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J98" t="n">
         <v>11</v>
@@ -7300,18 +7300,18 @@
           <t>방수진_v50.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G99" t="n">
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
         <v>4</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J99" t="n">
         <v>11</v>
@@ -7360,18 +7360,18 @@
           <t>방수진_v50.0_Tconcat_step</t>
         </is>
       </c>
-      <c r="G100" t="n">
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
         <v>4</v>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
       </c>
       <c r="J100" t="n">
         <v>12</v>
